--- a/data/trans_orig/P05A_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P05A_R-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>38194</t>
+          <t>38661</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>64098</t>
+          <t>64988</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>32976</t>
+          <t>32889</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>57657</t>
+          <t>56960</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>77394</t>
+          <t>79391</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>112874</t>
+          <t>114585</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,46%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>208912</t>
+          <t>208022</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>234816</t>
+          <t>234349</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,52%</t>
+          <t>76,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>85,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>203181</t>
+          <t>203878</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>227862</t>
+          <t>227949</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,9%</t>
+          <t>78,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>420974</t>
+          <t>419263</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>456454</t>
+          <t>454457</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,86%</t>
+          <t>78,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>85,13%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>140942</t>
+          <t>140483</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>184478</t>
+          <t>185279</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>160054</t>
+          <t>157732</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>204013</t>
+          <t>202062</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>40,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>313175</t>
+          <t>313621</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>375643</t>
+          <t>376420</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>31,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>37,75%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>308597</t>
+          <t>307796</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>352133</t>
+          <t>352592</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,59%</t>
+          <t>62,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,42%</t>
+          <t>71,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>299936</t>
+          <t>301887</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>343895</t>
+          <t>346217</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,52%</t>
+          <t>59,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,24%</t>
+          <t>68,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>621381</t>
+          <t>620604</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>683849</t>
+          <t>683403</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,32%</t>
+          <t>62,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,59%</t>
+          <t>68,54%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>55010</t>
+          <t>55553</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>84761</t>
+          <t>84848</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>113525</t>
+          <t>111816</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>147449</t>
+          <t>146599</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>33,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,96%</t>
+          <t>43,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>176469</t>
+          <t>175881</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>223769</t>
+          <t>222239</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>33,97%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>234085</t>
+          <t>233998</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>263836</t>
+          <t>263293</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>73,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,75%</t>
+          <t>82,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>187963</t>
+          <t>188813</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>221887</t>
+          <t>223596</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>56,04%</t>
+          <t>56,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>66,15%</t>
+          <t>66,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>430489</t>
+          <t>432019</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>477789</t>
+          <t>478377</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>65,8%</t>
+          <t>66,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,03%</t>
+          <t>73,12%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>89387</t>
+          <t>90029</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>123260</t>
+          <t>122644</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>76600</t>
+          <t>75420</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>109384</t>
+          <t>108658</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>174053</t>
+          <t>173245</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>219860</t>
+          <t>220651</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>30,22%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>235411</t>
+          <t>236027</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>269284</t>
+          <t>268642</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>65,63%</t>
+          <t>65,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,08%</t>
+          <t>74,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>262072</t>
+          <t>262798</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>294856</t>
+          <t>296036</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>70,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,38%</t>
+          <t>79,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>510267</t>
+          <t>509476</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>556074</t>
+          <t>556882</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,89%</t>
+          <t>69,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,16%</t>
+          <t>76,27%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>81077</t>
+          <t>81552</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>109891</t>
+          <t>109992</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>40,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>54,05%</t>
+          <t>54,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>79910</t>
+          <t>78193</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>106884</t>
+          <t>106646</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>37,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>51,47%</t>
+          <t>51,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>167946</t>
+          <t>166701</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>209088</t>
+          <t>206846</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>40,87%</t>
+          <t>40,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>50,88%</t>
+          <t>50,33%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>93417</t>
+          <t>93316</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>122231</t>
+          <t>121756</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>45,95%</t>
+          <t>45,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>60,12%</t>
+          <t>59,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>100784</t>
+          <t>101022</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>127758</t>
+          <t>129475</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>48,53%</t>
+          <t>48,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>61,52%</t>
+          <t>62,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>201888</t>
+          <t>204130</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>243030</t>
+          <t>244275</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>49,12%</t>
+          <t>49,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>59,13%</t>
+          <t>59,44%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>33659</t>
+          <t>34693</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>57101</t>
+          <t>58169</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>65265</t>
+          <t>64622</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>94364</t>
+          <t>95235</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>105367</t>
+          <t>105182</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>144450</t>
+          <t>143936</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>26,22%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>213710</t>
+          <t>212642</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>237152</t>
+          <t>236118</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>78,52%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>87,19%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>183780</t>
+          <t>182909</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>212879</t>
+          <t>213522</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>66,07%</t>
+          <t>65,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>76,54%</t>
+          <t>76,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>404505</t>
+          <t>405019</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>443588</t>
+          <t>443773</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>73,69%</t>
+          <t>73,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>80,81%</t>
+          <t>80,84%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>123723</t>
+          <t>121052</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>167245</t>
+          <t>167965</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>186153</t>
+          <t>187830</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>233653</t>
+          <t>237671</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>37,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>325475</t>
+          <t>319468</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>391073</t>
+          <t>385772</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>30,78%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>447782</t>
+          <t>447062</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>491304</t>
+          <t>493975</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>72,81%</t>
+          <t>72,69%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>80,32%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>404566</t>
+          <t>400548</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>452066</t>
+          <t>450389</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>63,39%</t>
+          <t>62,76%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>70,83%</t>
+          <t>70,57%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>862173</t>
+          <t>867474</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>927771</t>
+          <t>933778</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>69,22%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>74,03%</t>
+          <t>74,51%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>266887</t>
+          <t>266176</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>319913</t>
+          <t>319703</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>42,98%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>306645</t>
+          <t>306272</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>362405</t>
+          <t>362399</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>39,09%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>589087</t>
+          <t>587349</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>665619</t>
+          <t>665899</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>38,46%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>43,58%</t>
+          <t>43,6%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>423882</t>
+          <t>424092</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>476908</t>
+          <t>477619</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>56,99%</t>
+          <t>57,02%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>64,12%</t>
+          <t>64,21%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>421106</t>
+          <t>421112</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>476866</t>
+          <t>477239</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3302,7 +3302,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>60,86%</t>
+          <t>60,91%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>861687</t>
+          <t>861407</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>938219</t>
+          <t>939957</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>56,42%</t>
+          <t>56,4%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>61,43%</t>
+          <t>61,54%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>919208</t>
+          <t>920308</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1028197</t>
+          <t>1021510</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1107855</t>
+          <t>1111094</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1219558</t>
+          <t>1220849</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>36,13%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2057115</t>
+          <t>2048095</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2216172</t>
+          <t>2207510</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>33,17%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2248346</t>
+          <t>2255033</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2357335</t>
+          <t>2356235</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>68,62%</t>
+          <t>68,82%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>71,95%</t>
+          <t>71,91%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2159639</t>
+          <t>2158348</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2271342</t>
+          <t>2268103</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>63,91%</t>
+          <t>63,87%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>67,22%</t>
+          <t>67,12%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4439569</t>
+          <t>4448231</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4598626</t>
+          <t>4607646</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>66,83%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>69,09%</t>
+          <t>69,23%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>113659</t>
+          <t>114267</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>149039</t>
+          <t>148618</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>39,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>51,14%</t>
+          <t>50,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>111108</t>
+          <t>110651</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>145889</t>
+          <t>147071</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>39,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>51,48%</t>
+          <t>51,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>235371</t>
+          <t>235519</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>283984</t>
+          <t>286595</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>49,86%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>142405</t>
+          <t>142826</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>177785</t>
+          <t>177177</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>48,86%</t>
+          <t>49,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>61,0%</t>
+          <t>60,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>137475</t>
+          <t>136293</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>172256</t>
+          <t>172713</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>48,52%</t>
+          <t>48,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>60,79%</t>
+          <t>60,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>290824</t>
+          <t>288213</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>339437</t>
+          <t>339289</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>50,59%</t>
+          <t>50,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>59,05%</t>
+          <t>59,03%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>172948</t>
+          <t>174901</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>220558</t>
+          <t>221521</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,63%</t>
+          <t>43,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>198873</t>
+          <t>196961</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>244702</t>
+          <t>243331</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,72%</t>
+          <t>46,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>381873</t>
+          <t>379134</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>448745</t>
+          <t>445741</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>37,1%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>43,31%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>284969</t>
+          <t>284006</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>332579</t>
+          <t>330626</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>56,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>65,79%</t>
+          <t>65,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>279063</t>
+          <t>280434</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>324892</t>
+          <t>326804</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>53,28%</t>
+          <t>53,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>62,03%</t>
+          <t>62,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>580547</t>
+          <t>583551</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>647419</t>
+          <t>650158</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>56,4%</t>
+          <t>56,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>62,9%</t>
+          <t>63,17%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>128918</t>
+          <t>128278</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>163562</t>
+          <t>165827</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>39,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>50,62%</t>
+          <t>51,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>160725</t>
+          <t>158626</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>198490</t>
+          <t>197513</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>47,13%</t>
+          <t>46,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>58,2%</t>
+          <t>57,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>299929</t>
+          <t>299845</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>352636</t>
+          <t>351114</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>45,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,1%</t>
+          <t>52,87%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>159532</t>
+          <t>157267</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>194176</t>
+          <t>194816</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49,38%</t>
+          <t>48,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>60,1%</t>
+          <t>60,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>142530</t>
+          <t>143507</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>180295</t>
+          <t>182394</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>41,8%</t>
+          <t>42,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>52,87%</t>
+          <t>53,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>311478</t>
+          <t>313000</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>364185</t>
+          <t>364269</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>46,9%</t>
+          <t>47,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>54,84%</t>
+          <t>54,85%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>103844</t>
+          <t>105569</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>143154</t>
+          <t>142699</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>38,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>139641</t>
+          <t>139604</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>179185</t>
+          <t>177348</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>46,3%</t>
+          <t>45,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>253446</t>
+          <t>252176</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>308575</t>
+          <t>308884</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>40,65%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>229660</t>
+          <t>230115</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>268970</t>
+          <t>267245</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>61,6%</t>
+          <t>61,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>72,15%</t>
+          <t>71,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>207796</t>
+          <t>209633</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>247340</t>
+          <t>247377</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,7 +5248,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>53,7%</t>
+          <t>54,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>451221</t>
+          <t>450912</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>506350</t>
+          <t>507620</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>59,39%</t>
+          <t>59,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,64%</t>
+          <t>66,81%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>132421</t>
+          <t>132788</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>160008</t>
+          <t>160999</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>62,28%</t>
+          <t>62,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>75,26%</t>
+          <t>75,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>121422</t>
+          <t>121262</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>150868</t>
+          <t>149682</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>55,29%</t>
+          <t>55,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>68,7%</t>
+          <t>68,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>263076</t>
+          <t>262618</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>302553</t>
+          <t>303113</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>60,87%</t>
+          <t>60,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>70,0%</t>
+          <t>70,13%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>52610</t>
+          <t>51619</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>80197</t>
+          <t>79830</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>68723</t>
+          <t>69909</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>98169</t>
+          <t>98329</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>44,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>129656</t>
+          <t>129096</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>169133</t>
+          <t>169591</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>39,13%</t>
+          <t>39,24%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>121460</t>
+          <t>124431</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>156040</t>
+          <t>157567</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>44,33%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>56,95%</t>
+          <t>57,51%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>105228</t>
+          <t>104447</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>138459</t>
+          <t>138679</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>37,3%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>49,44%</t>
+          <t>49,52%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>238741</t>
+          <t>235394</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>286233</t>
+          <t>287401</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>43,09%</t>
+          <t>42,49%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>51,88%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>117941</t>
+          <t>116414</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>152521</t>
+          <t>149550</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>42,49%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>54,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>141572</t>
+          <t>141352</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>174803</t>
+          <t>175584</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>50,48%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>62,42%</t>
+          <t>62,7%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>267779</t>
+          <t>266611</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>315271</t>
+          <t>318618</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>48,33%</t>
+          <t>48,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>56,91%</t>
+          <t>57,51%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>251860</t>
+          <t>254076</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>304570</t>
+          <t>305532</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>38,33%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>45,95%</t>
+          <t>46,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>251382</t>
+          <t>253297</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>306417</t>
+          <t>306445</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>36,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>44,17%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>519854</t>
+          <t>518869</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>593360</t>
+          <t>591658</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>38,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>43,74%</t>
+          <t>43,61%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>358218</t>
+          <t>357256</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>410928</t>
+          <t>408712</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>54,05%</t>
+          <t>53,9%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>62,0%</t>
+          <t>61,67%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>387436</t>
+          <t>387408</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>442471</t>
+          <t>440556</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>55,84%</t>
+          <t>55,83%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>63,77%</t>
+          <t>63,49%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>763281</t>
+          <t>764983</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>836787</t>
+          <t>837772</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>56,26%</t>
+          <t>56,39%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>61,68%</t>
+          <t>61,75%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>170193</t>
+          <t>171870</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>218796</t>
+          <t>222745</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>165029</t>
+          <t>170815</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>219285</t>
+          <t>219906</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>353225</t>
+          <t>357125</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>425480</t>
+          <t>429583</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,8%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>560302</t>
+          <t>556353</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>608905</t>
+          <t>607228</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>71,92%</t>
+          <t>71,41%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>78,16%</t>
+          <t>77,94%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>604568</t>
+          <t>603947</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>658824</t>
+          <t>653038</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>73,38%</t>
+          <t>73,31%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>79,97%</t>
+          <t>79,27%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1177471</t>
+          <t>1173368</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1249726</t>
+          <t>1245826</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>73,46%</t>
+          <t>73,2%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>77,96%</t>
+          <t>77,72%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1300708</t>
+          <t>1298317</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1414412</t>
+          <t>1417843</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>37,95%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>41,34%</t>
+          <t>41,44%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1359477</t>
+          <t>1359339</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1478927</t>
+          <t>1479418</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>38,26%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>41,64%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2690560</t>
+          <t>2683574</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2866196</t>
+          <t>2858180</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>38,48%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>41,1%</t>
+          <t>40,98%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2006953</t>
+          <t>2003522</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2120657</t>
+          <t>2123048</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>58,66%</t>
+          <t>58,56%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>61,98%</t>
+          <t>62,05%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2073531</t>
+          <t>2073040</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2192981</t>
+          <t>2193119</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>58,37%</t>
+          <t>58,36%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>61,73%</t>
+          <t>61,74%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4107627</t>
+          <t>4115643</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4283263</t>
+          <t>4290249</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>58,9%</t>
+          <t>59,02%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>61,42%</t>
+          <t>61,52%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>91108</t>
+          <t>89857</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>125775</t>
+          <t>123980</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>42,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>123482</t>
+          <t>122478</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>157700</t>
+          <t>157982</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>42,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>54,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>223992</t>
+          <t>222301</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>272893</t>
+          <t>272351</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>38,46%</t>
+          <t>38,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>46,85%</t>
+          <t>46,76%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>167986</t>
+          <t>169781</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>202653</t>
+          <t>203904</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>57,18%</t>
+          <t>57,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>68,99%</t>
+          <t>69,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>131003</t>
+          <t>130721</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>165221</t>
+          <t>166225</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>45,38%</t>
+          <t>45,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>57,23%</t>
+          <t>57,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>309571</t>
+          <t>310113</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>358472</t>
+          <t>360163</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>53,15%</t>
+          <t>53,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>61,54%</t>
+          <t>61,83%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>251299</t>
+          <t>250715</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>295872</t>
+          <t>296757</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>49,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>58,87%</t>
+          <t>59,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>245347</t>
+          <t>245760</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>294277</t>
+          <t>294134</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>46,9%</t>
+          <t>46,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>56,26%</t>
+          <t>56,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>512481</t>
+          <t>512522</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>579263</t>
+          <t>577705</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7812,7 +7812,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>56,48%</t>
+          <t>56,33%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>206703</t>
+          <t>205818</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>251276</t>
+          <t>251860</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>41,13%</t>
+          <t>40,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>50,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>228807</t>
+          <t>228950</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>277737</t>
+          <t>277324</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>43,74%</t>
+          <t>43,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>53,1%</t>
+          <t>53,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>446396</t>
+          <t>447954</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>513178</t>
+          <t>513137</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,7 +7920,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>43,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>82759</t>
+          <t>83101</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>115002</t>
+          <t>116089</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>36,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>79849</t>
+          <t>78057</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>113335</t>
+          <t>112233</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>172555</t>
+          <t>170748</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>218428</t>
+          <t>217197</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>33,17%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>203563</t>
+          <t>202476</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>235806</t>
+          <t>235464</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,9%</t>
+          <t>63,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>73,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>222974</t>
+          <t>224076</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>256460</t>
+          <t>258252</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,3%</t>
+          <t>66,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,26%</t>
+          <t>76,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>436446</t>
+          <t>437677</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>482319</t>
+          <t>484126</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,65%</t>
+          <t>66,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,65%</t>
+          <t>73,93%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>96491</t>
+          <t>97771</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>133821</t>
+          <t>134576</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>36,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>122274</t>
+          <t>119244</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>160701</t>
+          <t>158972</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>41,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>229959</t>
+          <t>228085</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>282008</t>
+          <t>282254</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>37,34%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>234876</t>
+          <t>234121</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>272206</t>
+          <t>270926</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>63,7%</t>
+          <t>63,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,83%</t>
+          <t>73,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>226582</t>
+          <t>228311</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>265009</t>
+          <t>268039</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,51%</t>
+          <t>58,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,43%</t>
+          <t>69,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>473972</t>
+          <t>473726</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>526021</t>
+          <t>527895</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,7%</t>
+          <t>62,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,58%</t>
+          <t>69,83%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>37711</t>
+          <t>37317</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>61798</t>
+          <t>60610</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>40835</t>
+          <t>40840</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>65505</t>
+          <t>66608</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8806,7 +8806,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>85414</t>
+          <t>85825</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>119024</t>
+          <t>118823</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,65%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>149423</t>
+          <t>150611</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>173510</t>
+          <t>173904</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,74%</t>
+          <t>71,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,15%</t>
+          <t>82,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>153082</t>
+          <t>151979</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>177752</t>
+          <t>177747</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,7 +8914,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>70,03%</t>
+          <t>69,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>310784</t>
+          <t>310985</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>344394</t>
+          <t>343983</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>72,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,13%</t>
+          <t>80,03%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>88474</t>
+          <t>89066</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>121202</t>
+          <t>121530</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>46,06%</t>
+          <t>46,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>74578</t>
+          <t>72848</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>104600</t>
+          <t>105578</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>38,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>168689</t>
+          <t>171157</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>215544</t>
+          <t>216802</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>40,27%</t>
+          <t>40,51%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>141921</t>
+          <t>141593</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>174649</t>
+          <t>174057</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>53,94%</t>
+          <t>53,81%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>66,38%</t>
+          <t>66,15%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>167480</t>
+          <t>166502</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>197502</t>
+          <t>199232</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>61,56%</t>
+          <t>61,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>72,59%</t>
+          <t>73,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>319659</t>
+          <t>318401</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>366514</t>
+          <t>364046</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>59,73%</t>
+          <t>59,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>68,48%</t>
+          <t>68,02%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>228751</t>
+          <t>229603</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>279358</t>
+          <t>283113</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>34,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>42,55%</t>
+          <t>43,12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>254425</t>
+          <t>253845</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>306420</t>
+          <t>308405</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>36,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>497592</t>
+          <t>499063</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>571199</t>
+          <t>573639</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>37,06%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>42,6%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>377200</t>
+          <t>373445</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>427807</t>
+          <t>426955</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>57,45%</t>
+          <t>56,88%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>65,16%</t>
+          <t>65,03%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>383603</t>
+          <t>381618</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>435598</t>
+          <t>436178</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>55,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>63,13%</t>
+          <t>63,21%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>775382</t>
+          <t>772942</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>848989</t>
+          <t>847518</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>57,58%</t>
+          <t>57,4%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>63,05%</t>
+          <t>62,94%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>191456</t>
+          <t>193445</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>246306</t>
+          <t>242779</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>202726</t>
+          <t>202948</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>252509</t>
+          <t>255198</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>408937</t>
+          <t>409890</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>483201</t>
+          <t>482371</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>30,06%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>532277</t>
+          <t>535804</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>587127</t>
+          <t>585138</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>68,82%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>75,15%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>573658</t>
+          <t>570969</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>623441</t>
+          <t>623219</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>69,44%</t>
+          <t>69,11%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>75,46%</t>
+          <t>75,44%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1121549</t>
+          <t>1122379</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1195813</t>
+          <t>1194860</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>69,89%</t>
+          <t>69,94%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>74,52%</t>
+          <t>74,46%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1165437</t>
+          <t>1164617</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1276521</t>
+          <t>1275558</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>37,62%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1235034</t>
+          <t>1236745</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1354433</t>
+          <t>1356620</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>34,91%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>38,3%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2438907</t>
+          <t>2437893</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2595963</t>
+          <t>2595935</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,7 +10208,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2116562</t>
+          <t>2117525</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2227646</t>
+          <t>2228466</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>62,38%</t>
+          <t>62,41%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>65,65%</t>
+          <t>65,68%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2187803</t>
+          <t>2185616</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2307202</t>
+          <t>2305491</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>61,76%</t>
+          <t>61,7%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>65,13%</t>
+          <t>65,09%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4339356</t>
+          <t>4339384</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4496412</t>
+          <t>4497426</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>64,83%</t>
+          <t>64,85%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>9505</t>
+          <t>11220</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4389</t>
+          <t>5599</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20264</t>
+          <t>18977</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>10670</t>
+          <t>12268</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6691</t>
+          <t>7333</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16903</t>
+          <t>18750</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>20175</t>
+          <t>23488</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13493</t>
+          <t>15746</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33772</t>
+          <t>32222</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>301938</t>
+          <t>307625</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>291179</t>
+          <t>299868</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>307054</t>
+          <t>313246</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>278965</t>
+          <t>303793</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>272732</t>
+          <t>297311</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>282944</t>
+          <t>308728</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>580902</t>
+          <t>611418</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>567305</t>
+          <t>602684</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>587584</t>
+          <t>619160</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,52%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>75581</t>
+          <t>76550</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>57211</t>
+          <t>58879</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>101941</t>
+          <t>98332</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,17 +11075,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>68843</t>
+          <t>73053</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>56374</t>
+          <t>58805</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>84771</t>
+          <t>87842</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>144424</t>
+          <t>149604</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>121037</t>
+          <t>123588</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>175189</t>
+          <t>176793</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,41%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>442809</t>
+          <t>454097</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>416449</t>
+          <t>432315</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>461179</t>
+          <t>471768</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>85,57%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,34%</t>
+          <t>81,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>88,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,17 +11188,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>446126</t>
+          <t>473441</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>430198</t>
+          <t>458652</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>458595</t>
+          <t>487689</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,54%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>888935</t>
+          <t>927537</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>858170</t>
+          <t>900348</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>912322</t>
+          <t>953553</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>83,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>88,53%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>75131</t>
+          <t>75012</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>61320</t>
+          <t>61417</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>90829</t>
+          <t>89458</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>75185</t>
+          <t>77793</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>63745</t>
+          <t>65539</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>91213</t>
+          <t>91968</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>150316</t>
+          <t>152805</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>131851</t>
+          <t>134601</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>169283</t>
+          <t>174039</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,88%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>240919</t>
+          <t>240981</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>225221</t>
+          <t>226535</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>254730</t>
+          <t>254576</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>76,23%</t>
+          <t>76,26%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,26%</t>
+          <t>71,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>80,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>273943</t>
+          <t>278588</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>257915</t>
+          <t>264413</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>285383</t>
+          <t>290842</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>78,46%</t>
+          <t>78,17%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>73,87%</t>
+          <t>74,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>81,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>514862</t>
+          <t>519570</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>495895</t>
+          <t>498336</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>533327</t>
+          <t>537774</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>77,4%</t>
+          <t>77,27%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,55%</t>
+          <t>74,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>80,18%</t>
+          <t>79,98%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>64682</t>
+          <t>70775</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>48807</t>
+          <t>54030</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>82912</t>
+          <t>93201</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>78372</t>
+          <t>88843</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>48808</t>
+          <t>73266</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>104928</t>
+          <t>106701</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>143054</t>
+          <t>159619</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>102333</t>
+          <t>137955</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>171362</t>
+          <t>189421</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>23,84%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>247875</t>
+          <t>302370</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>229645</t>
+          <t>279944</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>263750</t>
+          <t>319115</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>81,03%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,47%</t>
+          <t>75,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,38%</t>
+          <t>85,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>396733</t>
+          <t>332433</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>370177</t>
+          <t>314575</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>426297</t>
+          <t>348010</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>78,91%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,91%</t>
+          <t>74,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>82,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>644608</t>
+          <t>634802</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>616300</t>
+          <t>605000</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>685329</t>
+          <t>656466</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>81,84%</t>
+          <t>79,91%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>76,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>82,63%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475105</t>
+          <t>421276</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475105</t>
+          <t>421276</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475105</t>
+          <t>421276</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>787662</t>
+          <t>794421</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>787662</t>
+          <t>794421</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>787662</t>
+          <t>794421</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>8461</t>
+          <t>12080</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4686</t>
+          <t>6858</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14090</t>
+          <t>19886</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,17 +12104,17 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>5248</t>
+          <t>4642</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1904</t>
+          <t>2484</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11638</t>
+          <t>8836</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>13709</t>
+          <t>16723</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7796</t>
+          <t>10984</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21842</t>
+          <t>25257</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,81%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>170281</t>
+          <t>193585</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>164652</t>
+          <t>185779</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>174056</t>
+          <t>198807</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,17 +12217,17 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>253531</t>
+          <t>224276</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>247141</t>
+          <t>220082</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>256875</t>
+          <t>226434</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>423812</t>
+          <t>417859</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>415679</t>
+          <t>409325</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>429725</t>
+          <t>423598</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>97,47%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>52019</t>
+          <t>50814</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>40952</t>
+          <t>39874</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>64795</t>
+          <t>63176</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>53145</t>
+          <t>55086</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>43608</t>
+          <t>45839</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>63896</t>
+          <t>66868</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>105164</t>
+          <t>105899</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>91041</t>
+          <t>92008</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>121367</t>
+          <t>123349</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>23,08%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>217617</t>
+          <t>219893</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>204841</t>
+          <t>207531</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>228684</t>
+          <t>230833</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>81,23%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>75,97%</t>
+          <t>76,66%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,81%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>203911</t>
+          <t>208664</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>193160</t>
+          <t>196882</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>213448</t>
+          <t>217911</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>79,33%</t>
+          <t>79,11%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>75,14%</t>
+          <t>74,65%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>82,62%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>421528</t>
+          <t>428558</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>405325</t>
+          <t>411108</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>435651</t>
+          <t>442449</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>80,03%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>76,96%</t>
+          <t>76,92%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>82,78%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>203878</t>
+          <t>231614</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>177880</t>
+          <t>206141</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>234147</t>
+          <t>263471</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>36,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>437022</t>
+          <t>270967</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>298449</t>
+          <t>246992</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>639146</t>
+          <t>298126</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>75,32%</t>
+          <t>38,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>640900</t>
+          <t>502580</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>497639</t>
+          <t>465291</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1001261</t>
+          <t>543568</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>43,53%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>68,0%</t>
+          <t>36,51%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>420073</t>
+          <t>485777</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>389804</t>
+          <t>453920</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>446071</t>
+          <t>511250</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>67,32%</t>
+          <t>67,71%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>62,47%</t>
+          <t>63,27%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>71,49%</t>
+          <t>71,27%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>411513</t>
+          <t>500344</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>209389</t>
+          <t>473185</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>550086</t>
+          <t>524319</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>64,87%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>61,35%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>64,83%</t>
+          <t>67,98%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>831586</t>
+          <t>986122</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>471225</t>
+          <t>945134</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>974847</t>
+          <t>1023411</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>56,47%</t>
+          <t>66,24%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>63,49%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>66,2%</t>
+          <t>68,75%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>623951</t>
+          <t>717391</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>623951</t>
+          <t>717391</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>623951</t>
+          <t>717391</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>848535</t>
+          <t>771311</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>848535</t>
+          <t>771311</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>848535</t>
+          <t>771311</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1472486</t>
+          <t>1488702</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1472486</t>
+          <t>1488702</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1472486</t>
+          <t>1488702</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>105342</t>
+          <t>126928</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>46908</t>
+          <t>105309</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>152406</t>
+          <t>148022</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>146601</t>
+          <t>178654</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>129185</t>
+          <t>158534</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>165504</t>
+          <t>201998</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>251943</t>
+          <t>305582</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>163650</t>
+          <t>274808</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>307630</t>
+          <t>336035</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>20,62%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>823378</t>
+          <t>671144</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>776314</t>
+          <t>650050</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>881812</t>
+          <t>692763</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>84,1%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>86,8%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>571130</t>
+          <t>652677</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>552227</t>
+          <t>629333</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>588546</t>
+          <t>672797</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>79,57%</t>
+          <t>78,51%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>76,94%</t>
+          <t>75,7%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>80,93%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1394509</t>
+          <t>1323821</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1338822</t>
+          <t>1293368</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1482802</t>
+          <t>1354595</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>84,7%</t>
+          <t>81,25%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>81,32%</t>
+          <t>79,38%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>83,13%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>594599</t>
+          <t>654993</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>466842</t>
+          <t>602590</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>661663</t>
+          <t>704913</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>875086</t>
+          <t>761307</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>695495</t>
+          <t>722211</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1443886</t>
+          <t>810247</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1469685</t>
+          <t>1416300</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1260212</t>
+          <t>1351245</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2067857</t>
+          <t>1485075</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>20,44%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2864890</t>
+          <t>2875473</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2797826</t>
+          <t>2825553</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2992647</t>
+          <t>2927876</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>82,81%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>80,87%</t>
+          <t>80,03%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>82,93%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2835852</t>
+          <t>2974216</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2267052</t>
+          <t>2925276</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3015443</t>
+          <t>3013312</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>76,42%</t>
+          <t>79,62%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>61,09%</t>
+          <t>78,31%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>81,26%</t>
+          <t>80,67%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>5700741</t>
+          <t>5849689</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5102569</t>
+          <t>5780914</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5910214</t>
+          <t>5914744</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>79,5%</t>
+          <t>80,51%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>71,16%</t>
+          <t>79,56%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>81,4%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3459489</t>
+          <t>3530466</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3459489</t>
+          <t>3530466</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3459489</t>
+          <t>3530466</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3710938</t>
+          <t>3735523</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3710938</t>
+          <t>3735523</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3710938</t>
+          <t>3735523</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7170426</t>
+          <t>7265989</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7170426</t>
+          <t>7265989</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7170426</t>
+          <t>7265989</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
